--- a/analytics/data/processed/desempenho_empacotamento_diario.xlsx
+++ b/analytics/data/processed/desempenho_empacotamento_diario.xlsx
@@ -16,17 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,39 +37,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -78,9 +51,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -446,494 +417,724 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>OP Vertech</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Data Wht (dia)</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>Maquina</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Prefixo</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Objetivo %</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Empacotado %</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Rejeição %</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Emp - Rejeitado %</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>198135</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>SB -1036-SWN</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.8746246246246249</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8746246246246249</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>198176</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LB -0478-N1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>198456</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LB -0491-N1</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.773888888888889</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.773888888888889</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>198546</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MB -1585-S</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7327913279132793</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.05962059620596209</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6891018720485309</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>198567</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SB -1037-SWN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.7962962962962963</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>198592</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>MB -1512-SN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6870993589743589</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.6870993589743589</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>198594</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>MB -1398-S</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="E8" t="n">
         <v>0.6</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F8" t="n">
         <v>0.5895833333333333</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G8" t="n">
         <v>0.25</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H8" t="n">
         <v>0.4421875</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>198613</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SB -1471-SN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6105301779490001</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.09392771968446173</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.553184470535702</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>198618</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>SB -1035-SWN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.8914583333333334</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8914583333333334</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>198639</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>SB -1290-S</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.9379132231404957</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9379132231404957</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>198645</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>SB -1579-N1N</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.9287990196078434</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.9287990196078434</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>198658</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LB -0502-S</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7080078125</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.41015625</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4176139831542969</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>198659</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>SB -1348-S</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.9383730158730156</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.9383730158730156</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>198660</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>LB -0586-S</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="E15" t="n">
         <v>0.55</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F15" t="n">
         <v>0.642948717948718</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G15" t="n">
         <v>0.08076923076923075</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H15" t="n">
         <v>0.591018244575937</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>MB -1512-SN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.6870993589743589</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.6870993589743589</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>LB -0478-N1</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>198663</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>SB -0019-N1D</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.946666666666667</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.946666666666667</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>198693</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PL -5814-</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.8712654320987654</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8712654320987654</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>198694</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>SB -1704-S</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.6</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.6197916666666666</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.6197916666666666</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>LB -0491-N1</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.773888888888889</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.773888888888889</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>SB -1035-SWN</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.8914583333333334</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8914583333333334</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="F18" t="n">
+        <v>0.654040404040404</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1841329966329966</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.5336099845253885</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>198698</t>
+        </is>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>A2</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>SB -1036-SWN</t>
         </is>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="E19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" t="n">
         <v>0.3326984126984125</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
         <v>0.3326984126984125</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>SB -1037-SWN</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.7962962962962963</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.7962962962962963</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>SB -1036-SWN</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.8746246246246249</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8746246246246249</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>SB -1348-S</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.9383730158730156</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.9383730158730156</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>SB -1290-S</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.9379132231404957</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.9379132231404957</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>SB -1579-N1N</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.9287990196078434</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.9287990196078434</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>198701</t>
+        </is>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>B1</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>LB -0449-SX</t>
         </is>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.5209567075988645</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.1616161616161617</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.4367616841485429</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>SB -1704-S</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
+      <c r="E20" t="n">
         <v>0.6</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.654040404040404</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.1841329966329966</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.5336099845253885</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>LB -0502-S</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.7080078125</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.41015625</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.4176139831542969</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>SB -0019-N1D</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.946666666666667</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.946666666666667</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n"/>
-      <c r="B18" s="1" t="inlineStr">
-        <is>
-          <t>SB -1471-SN</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>0.6105301779490001</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.09392771968446173</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.553184470535702</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="B19" s="1" t="inlineStr">
-        <is>
-          <t>PL -5814-</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.8712654320987654</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.8712654320987654</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>MB -1585-S</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.7327913279132793</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.05962059620596209</v>
-      </c>
       <c r="F20" t="n">
-        <v>0.6891018720485309</v>
+        <v>0.3893939393939392</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6666666666666675</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1297979797979794</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>198704</t>
+        </is>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LB -0449-SX</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.4692513368983957</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.09324009324009307</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4254982984929509</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>198707</t>
+        </is>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LB -0449-SX</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6921596921596922</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.6921596921596922</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="A8:A9"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>